--- a/output/casestudy_20260910.xlsx
+++ b/output/casestudy_20260910.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.436364899999717</v>
+        <v>10.78875789999984</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.479450599999836</v>
+        <v>11.7256440000001</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.143916300000001</v>
+        <v>7.691904600000271</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.652831000000333</v>
+        <v>12.87199799999962</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.34056400000009</v>
+        <v>13.31527730000016</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.048520700000154</v>
+        <v>11.15200999999979</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>9.947127199999613</v>
+        <v>16.18780040000001</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>9.995188700000199</v>
+        <v>13.07614590000048</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>13.6333724000001</v>
+        <v>15.38562350000029</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.143184900000051</v>
+        <v>7.807062700000643</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.158331199999793</v>
+        <v>7.33414619999985</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.4 초</t>
+          <t>10.8 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.5 초</t>
+          <t>11.7 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>7.7 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.7 초</t>
+          <t>12.9 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.3 초</t>
+          <t>13.3 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.0 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9.9 초</t>
+          <t>16.2 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.0 초</t>
+          <t>13.1 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13.6 초</t>
+          <t>15.4 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.1 초</t>
+          <t>7.8 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.2 초</t>
+          <t>7.3 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>106.9 초</t>
+          <t>135.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260910.xlsx
+++ b/output/casestudy_20260910.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.78875789999984</v>
+        <v>11.68646679999983</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.7256440000001</v>
+        <v>11.35247170000002</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.691904600000271</v>
+        <v>7.388992100000905</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>12.87199799999962</v>
+        <v>11.34645500000079</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>13.31527730000016</v>
+        <v>11.9277488000007</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.15200999999979</v>
+        <v>9.433670200000051</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>16.18780040000001</v>
+        <v>11.86195439999938</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>13.07614590000048</v>
+        <v>11.48416859999998</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>15.38562350000029</v>
+        <v>15.78076040000087</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.807062700000643</v>
+        <v>8.406487500000367</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.33414619999985</v>
+        <v>7.190062100000432</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.8 초</t>
+          <t>11.7 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.7 초</t>
+          <t>11.4 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.7 초</t>
+          <t>7.4 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.9 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.3 초</t>
+          <t>11.9 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>9.4 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.2 초</t>
+          <t>11.9 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13.1 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15.4 초</t>
+          <t>15.8 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.8 초</t>
+          <t>8.4 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.3 초</t>
+          <t>7.2 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>135.9 초</t>
+          <t>126.0 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260910.xlsx
+++ b/output/casestudy_20260910.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11.68646679999983</v>
+        <v>11.32757919999858</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.35247170000002</v>
+        <v>10.68944710000142</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.388992100000905</v>
+        <v>7.675502699999925</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.34645500000079</v>
+        <v>13.62343139999939</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.9277488000007</v>
+        <v>15.49796149999747</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.433670200000051</v>
+        <v>11.21502340000006</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11.86195439999938</v>
+        <v>14.75482730000294</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>11.48416859999998</v>
+        <v>13.39112030000251</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>15.78076040000087</v>
+        <v>15.66462870000032</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>8.406487500000367</v>
+        <v>10.06983680000121</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.190062100000432</v>
+        <v>8.696855499998492</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.7 초</t>
+          <t>11.3 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.4 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.4 초</t>
+          <t>7.7 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>13.6 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.9 초</t>
+          <t>15.5 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9.4 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.9 초</t>
+          <t>14.8 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11.5 초</t>
+          <t>13.4 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15.8 초</t>
+          <t>15.7 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8.4 초</t>
+          <t>10.1 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.2 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>126.0 초</t>
+          <t>141.6 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260910.xlsx
+++ b/output/casestudy_20260910.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11.32757919999858</v>
+        <v>15.52664589999767</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.68944710000142</v>
+        <v>15.68109080000067</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.675502699999925</v>
+        <v>9.566876299999421</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>13.62343139999939</v>
+        <v>15.62990150000041</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>15.49796149999747</v>
+        <v>15.97534459999952</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.21502340000006</v>
+        <v>13.48202259999744</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>14.75482730000294</v>
+        <v>16.54935570000089</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>13.39112030000251</v>
+        <v>15.93214570000055</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>15.66462870000032</v>
+        <v>18.84989439999845</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>10.06983680000121</v>
+        <v>9.548742999999376</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>8.696855499998492</v>
+        <v>8.516429499999504</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.3 초</t>
+          <t>15.5 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>15.7 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.7 초</t>
+          <t>9.6 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.6 초</t>
+          <t>15.6 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15.5 초</t>
+          <t>16.0 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>13.5 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14.8 초</t>
+          <t>16.5 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13.4 초</t>
+          <t>15.9 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15.7 초</t>
+          <t>18.8 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.1 초</t>
+          <t>9.5 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>8.5 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>141.6 초</t>
+          <t>165.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260910.xlsx
+++ b/output/casestudy_20260910.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>15.52664589999767</v>
+        <v>9.870070199998736</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15.68109080000067</v>
+        <v>9.703644500001246</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>9.566876299999421</v>
+        <v>6.331211799999437</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>15.62990150000041</v>
+        <v>9.965096100000665</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>15.97534459999952</v>
+        <v>10.70592889999898</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>13.48202259999744</v>
+        <v>8.341106600000785</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>16.54935570000089</v>
+        <v>10.30848650000189</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>15.93214570000055</v>
+        <v>10.35804629999984</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>18.84989439999845</v>
+        <v>15.13068439999915</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9.548742999999376</v>
+        <v>8.166614400000981</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>8.516429499999504</v>
+        <v>7.160942700000305</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.5 초</t>
+          <t>9.9 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.7 초</t>
+          <t>9.7 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>6.3 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.6 초</t>
+          <t>10.0 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16.0 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13.5 초</t>
+          <t>8.3 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16.5 초</t>
+          <t>10.3 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15.9 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18.8 초</t>
+          <t>15.1 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9.5 초</t>
+          <t>8.2 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8.5 초</t>
+          <t>7.2 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>165.4 초</t>
+          <t>113.7 초</t>
         </is>
       </c>
     </row>
